--- a/Comparison Excels/induc_compart.xlsx
+++ b/Comparison Excels/induc_compart.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/polatozturk/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/polatozturk/Desktop/EE568_Project_1/Comparison Excels/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E7B242C-7E36-2246-922B-6F7C95922DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05C5C102-574D-7E4F-B0DE-1C8D11949448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9280" yWindow="1360" windowWidth="26040" windowHeight="13980" xr2:uid="{1F7AAC66-2E43-AC45-BD80-79B4C290172D}"/>
+    <workbookView minimized="1" xWindow="5520" yWindow="11240" windowWidth="26040" windowHeight="13980" activeTab="1" xr2:uid="{1F7AAC66-2E43-AC45-BD80-79B4C290172D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
